--- a/outputs/list_of_stats.xlsx
+++ b/outputs/list_of_stats.xlsx
@@ -7022,7 +7022,7 @@
         <v>0.95</v>
       </c>
       <c r="C3" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
@@ -7036,13 +7036,13 @@
         <v>494</v>
       </c>
       <c r="B4" t="n">
-        <v>0.86</v>
+        <v>0.68</v>
       </c>
       <c r="C4" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.9</v>
+        <v>2.3</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
@@ -7056,7 +7056,7 @@
         <v>0.008</v>
       </c>
       <c r="C5" t="n">
-        <v>0.072</v>
+        <v>0.054</v>
       </c>
       <c r="D5" t="n">
         <v>-15</v>
@@ -7087,16 +7087,16 @@
         <v>497</v>
       </c>
       <c r="B7" t="n">
-        <v>0.099</v>
+        <v>0.0027</v>
       </c>
       <c r="C7" t="n">
-        <v>0.27</v>
+        <v>0.036</v>
       </c>
       <c r="D7" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="E7" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8">
@@ -7107,7 +7107,7 @@
         <v>0.77</v>
       </c>
       <c r="C8" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="D8" t="n">
         <v>-1.3</v>
@@ -7124,7 +7124,7 @@
         <v>0.59</v>
       </c>
       <c r="C9" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="D9" t="n">
         <v>-2.1</v>
@@ -7138,13 +7138,13 @@
         <v>500</v>
       </c>
       <c r="B10" t="n">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="C10" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8</v>
+        <v>-0.48</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
@@ -7158,7 +7158,7 @@
         <v>0.04</v>
       </c>
       <c r="C11" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="D11" t="n">
         <v>18</v>
@@ -7175,7 +7175,7 @@
         <v>0.37</v>
       </c>
       <c r="C12" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="D12" t="n">
         <v>4.6</v>
@@ -7189,13 +7189,13 @@
         <v>503</v>
       </c>
       <c r="B13" t="n">
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
       <c r="C13" t="n">
-        <v>0.89</v>
+        <v>0.99</v>
       </c>
       <c r="D13" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="E13" t="s">
         <v>14</v>
@@ -7209,7 +7209,7 @@
         <v>0.019</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1</v>
+        <v>0.087</v>
       </c>
       <c r="D14" t="n">
         <v>-17</v>
@@ -7226,7 +7226,7 @@
         <v>0.86</v>
       </c>
       <c r="C15" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="D15" t="n">
         <v>-1.5</v>
@@ -7243,7 +7243,7 @@
         <v>0.0047</v>
       </c>
       <c r="C16" t="n">
-        <v>0.063</v>
+        <v>0.042</v>
       </c>
       <c r="D16" t="n">
         <v>-26</v>
@@ -7260,7 +7260,7 @@
         <v>0.075</v>
       </c>
       <c r="C17" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="D17" t="n">
         <v>13</v>
@@ -7277,7 +7277,7 @@
         <v>0.0027</v>
       </c>
       <c r="C18" t="n">
-        <v>0.063</v>
+        <v>0.036</v>
       </c>
       <c r="D18" t="n">
         <v>-14</v>
@@ -7291,13 +7291,13 @@
         <v>509</v>
       </c>
       <c r="B19" t="n">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>0.06</v>
       </c>
       <c r="E19" t="s">
         <v>14</v>
@@ -7311,7 +7311,7 @@
         <v>0.59</v>
       </c>
       <c r="C20" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="D20" t="n">
         <v>3.7</v>
@@ -7328,7 +7328,7 @@
         <v>0.59</v>
       </c>
       <c r="C21" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="D21" t="n">
         <v>0.8</v>
@@ -7342,13 +7342,13 @@
         <v>512</v>
       </c>
       <c r="B22" t="n">
-        <v>0.86</v>
+        <v>0.68</v>
       </c>
       <c r="C22" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="D22" t="n">
-        <v>1.6</v>
+        <v>-4.8</v>
       </c>
       <c r="E22" t="s">
         <v>14</v>
@@ -7362,7 +7362,7 @@
         <v>0.37</v>
       </c>
       <c r="C23" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="D23" t="n">
         <v>0.24</v>
@@ -7379,7 +7379,7 @@
         <v>0.04</v>
       </c>
       <c r="C24" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="D24" t="n">
         <v>-0.47</v>
@@ -7393,13 +7393,13 @@
         <v>515</v>
       </c>
       <c r="B25" t="n">
-        <v>0.86</v>
+        <v>0.51</v>
       </c>
       <c r="C25" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="D25" t="n">
-        <v>0.078</v>
+        <v>-0.19</v>
       </c>
       <c r="E25" t="s">
         <v>14</v>
@@ -7413,7 +7413,7 @@
         <v>0.31</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="D26" t="n">
         <v>-0.98</v>
@@ -7430,7 +7430,7 @@
         <v>0.019</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1</v>
+        <v>0.087</v>
       </c>
       <c r="D27" t="n">
         <v>3.2</v>
@@ -7444,13 +7444,13 @@
         <v>518</v>
       </c>
       <c r="B28" t="n">
-        <v>0.44</v>
+        <v>0.25</v>
       </c>
       <c r="C28" t="n">
-        <v>0.79</v>
+        <v>0.57</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="E28" t="s">
         <v>14</v>
@@ -29793,7 +29793,7 @@
         <v>-0.788937590243313</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00079613804131788</v>
+        <v>0.000796138041317881</v>
       </c>
       <c r="E21" t="s">
         <v>706</v>
@@ -30065,7 +30065,7 @@
         <v>-0.564479289920568</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0354714527660497</v>
+        <v>0.0354714527660498</v>
       </c>
       <c r="E37" t="s">
         <v>706</v>
@@ -30643,7 +30643,7 @@
         <v>-0.486785174068561</v>
       </c>
       <c r="D71" t="n">
-        <v>0.0775234720111203</v>
+        <v>0.0775234720111202</v>
       </c>
       <c r="E71" t="s">
         <v>740</v>
@@ -31629,7 +31629,7 @@
         <v>0.791025907861412</v>
       </c>
       <c r="D129" t="n">
-        <v>0.000753691354034559</v>
+        <v>0.00075369135403456</v>
       </c>
       <c r="E129" t="s">
         <v>740</v>
@@ -33598,10 +33598,10 @@
         <v>742</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.00549450549450549</v>
+        <v>-0.302197802197802</v>
       </c>
       <c r="D245" t="n">
-        <v>0.992769768768747</v>
+        <v>0.315390822214927</v>
       </c>
       <c r="E245" t="s">
         <v>743</v>
@@ -33615,10 +33615,10 @@
         <v>744</v>
       </c>
       <c r="C246" t="n">
-        <v>0.362637362637363</v>
+        <v>0.0934065934065934</v>
       </c>
       <c r="D246" t="n">
-        <v>0.223986534640913</v>
+        <v>0.764581607054883</v>
       </c>
       <c r="E246" t="s">
         <v>743</v>
@@ -33632,10 +33632,10 @@
         <v>745</v>
       </c>
       <c r="C247" t="n">
-        <v>0.258241758241758</v>
+        <v>0.010989010989011</v>
       </c>
       <c r="D247" t="n">
-        <v>0.393835185104886</v>
+        <v>0.978311453941831</v>
       </c>
       <c r="E247" t="s">
         <v>743</v>
@@ -33649,10 +33649,10 @@
         <v>705</v>
       </c>
       <c r="C248" t="n">
-        <v>0.428571428571429</v>
+        <v>0.214285714285714</v>
       </c>
       <c r="D248" t="n">
-        <v>0.145930216094456</v>
+        <v>0.481851309334423</v>
       </c>
       <c r="E248" t="s">
         <v>743</v>
@@ -33666,10 +33666,10 @@
         <v>746</v>
       </c>
       <c r="C249" t="n">
-        <v>0.10989010989011</v>
+        <v>-0.186813186813187</v>
       </c>
       <c r="D249" t="n">
-        <v>0.723248148906413</v>
+        <v>0.541341049536417</v>
       </c>
       <c r="E249" t="s">
         <v>743</v>
@@ -33683,10 +33683,10 @@
         <v>742</v>
       </c>
       <c r="C250" t="n">
-        <v>-0.00549450549450549</v>
+        <v>0.307692307692308</v>
       </c>
       <c r="D250" t="n">
-        <v>0.992769768768747</v>
+        <v>0.306287043691456</v>
       </c>
       <c r="E250" t="s">
         <v>743</v>
@@ -33700,10 +33700,10 @@
         <v>744</v>
       </c>
       <c r="C251" t="n">
-        <v>0.0604395604395604</v>
+        <v>0.362637362637363</v>
       </c>
       <c r="D251" t="n">
-        <v>0.848988506886828</v>
+        <v>0.223986534640913</v>
       </c>
       <c r="E251" t="s">
         <v>743</v>
@@ -33717,10 +33717,10 @@
         <v>745</v>
       </c>
       <c r="C252" t="n">
-        <v>0.313186813186813</v>
+        <v>0.582417582417582</v>
       </c>
       <c r="D252" t="n">
-        <v>0.297341475651677</v>
+        <v>0.0402766973377868</v>
       </c>
       <c r="E252" t="s">
         <v>743</v>
@@ -33734,10 +33734,10 @@
         <v>705</v>
       </c>
       <c r="C253" t="n">
-        <v>0.197802197802198</v>
+        <v>0.461538461538462</v>
       </c>
       <c r="D253" t="n">
-        <v>0.517155182307656</v>
+        <v>0.114935670585034</v>
       </c>
       <c r="E253" t="s">
         <v>743</v>
@@ -33751,10 +33751,10 @@
         <v>746</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.241758241758242</v>
+        <v>0.032967032967033</v>
       </c>
       <c r="D254" t="n">
-        <v>0.425758800174325</v>
+        <v>0.920585447351698</v>
       </c>
       <c r="E254" t="s">
         <v>743</v>
@@ -33768,10 +33768,10 @@
         <v>742</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.362637362637363</v>
+        <v>-0.247252747252747</v>
       </c>
       <c r="D255" t="n">
-        <v>0.223986534640913</v>
+        <v>0.414969916573171</v>
       </c>
       <c r="E255" t="s">
         <v>743</v>
@@ -33785,10 +33785,10 @@
         <v>744</v>
       </c>
       <c r="C256" t="n">
-        <v>0.131868131868132</v>
+        <v>0.313186813186813</v>
       </c>
       <c r="D256" t="n">
-        <v>0.669269053658082</v>
+        <v>0.297341475651677</v>
       </c>
       <c r="E256" t="s">
         <v>743</v>
@@ -33802,10 +33802,10 @@
         <v>745</v>
       </c>
       <c r="C257" t="n">
-        <v>-0.126373626373626</v>
+        <v>-0.00549450549450549</v>
       </c>
       <c r="D257" t="n">
-        <v>0.682631671519805</v>
+        <v>0.992769768768747</v>
       </c>
       <c r="E257" t="s">
         <v>743</v>
@@ -33819,10 +33819,10 @@
         <v>705</v>
       </c>
       <c r="C258" t="n">
-        <v>0.230769230769231</v>
+        <v>0.406593406593407</v>
       </c>
       <c r="D258" t="n">
-        <v>0.447771588455077</v>
+        <v>0.169503997837466</v>
       </c>
       <c r="E258" t="s">
         <v>743</v>
@@ -33836,10 +33836,10 @@
         <v>746</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.313186813186813</v>
+        <v>-0.192307692307692</v>
       </c>
       <c r="D259" t="n">
-        <v>0.297341475651677</v>
+        <v>0.529184736920623</v>
       </c>
       <c r="E259" t="s">
         <v>743</v>
@@ -33853,10 +33853,10 @@
         <v>742</v>
       </c>
       <c r="C260" t="n">
-        <v>0.00549450549450549</v>
+        <v>0.0164835164835165</v>
       </c>
       <c r="D260" t="n">
-        <v>0.992769768768747</v>
+        <v>0.963859580344439</v>
       </c>
       <c r="E260" t="s">
         <v>743</v>
@@ -33870,10 +33870,10 @@
         <v>744</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.598901098901099</v>
+        <v>-0.565934065934066</v>
       </c>
       <c r="D261" t="n">
-        <v>0.0340306577688046</v>
+        <v>0.0473395951811578</v>
       </c>
       <c r="E261" t="s">
         <v>743</v>
@@ -33887,10 +33887,10 @@
         <v>745</v>
       </c>
       <c r="C262" t="n">
-        <v>-0.538461538461538</v>
+        <v>-0.543956043956044</v>
       </c>
       <c r="D262" t="n">
-        <v>0.0610936374942774</v>
+        <v>0.0581339946181927</v>
       </c>
       <c r="E262" t="s">
         <v>743</v>
@@ -33904,10 +33904,10 @@
         <v>705</v>
       </c>
       <c r="C263" t="n">
-        <v>-0.571428571428571</v>
+        <v>-0.538461538461538</v>
       </c>
       <c r="D263" t="n">
-        <v>0.04489072291451</v>
+        <v>0.0610936374942774</v>
       </c>
       <c r="E263" t="s">
         <v>743</v>
@@ -33921,10 +33921,10 @@
         <v>746</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.181318681318681</v>
+        <v>-0.142857142857143</v>
       </c>
       <c r="D264" t="n">
-        <v>0.553621558251875</v>
+        <v>0.642828942723202</v>
       </c>
       <c r="E264" t="s">
         <v>743</v>
@@ -33938,10 +33938,10 @@
         <v>742</v>
       </c>
       <c r="C265" t="n">
-        <v>0.335164835164835</v>
+        <v>0.340659340659341</v>
       </c>
       <c r="D265" t="n">
-        <v>0.263148014601437</v>
+        <v>0.254997689115259</v>
       </c>
       <c r="E265" t="s">
         <v>743</v>
@@ -33955,10 +33955,10 @@
         <v>744</v>
       </c>
       <c r="C266" t="n">
-        <v>0.241758241758242</v>
+        <v>0.247252747252747</v>
       </c>
       <c r="D266" t="n">
-        <v>0.425758800174326</v>
+        <v>0.414969916573171</v>
       </c>
       <c r="E266" t="s">
         <v>743</v>
@@ -33972,10 +33972,10 @@
         <v>745</v>
       </c>
       <c r="C267" t="n">
-        <v>0.461538461538462</v>
+        <v>0.478021978021978</v>
       </c>
       <c r="D267" t="n">
-        <v>0.114935670585034</v>
+        <v>0.101312257441764</v>
       </c>
       <c r="E267" t="s">
         <v>743</v>
@@ -33989,10 +33989,10 @@
         <v>705</v>
       </c>
       <c r="C268" t="n">
-        <v>0.351648351648352</v>
+        <v>0.357142857142857</v>
       </c>
       <c r="D268" t="n">
-        <v>0.23917453853646</v>
+        <v>0.231501302320309</v>
       </c>
       <c r="E268" t="s">
         <v>743</v>
@@ -34006,10 +34006,10 @@
         <v>746</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.00549450549450549</v>
+        <v>0</v>
       </c>
       <c r="D269" t="n">
-        <v>0.992769768768747</v>
+        <v>1</v>
       </c>
       <c r="E269" t="s">
         <v>743</v>
@@ -34023,10 +34023,10 @@
         <v>742</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.17032967032967</v>
+        <v>-0.0659340659340659</v>
       </c>
       <c r="D270" t="n">
-        <v>0.578544468706138</v>
+        <v>0.834785888052903</v>
       </c>
       <c r="E270" t="s">
         <v>743</v>
@@ -34040,10 +34040,10 @@
         <v>744</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.653846153846154</v>
+        <v>-0.60989010989011</v>
       </c>
       <c r="D271" t="n">
-        <v>0.0183248994068465</v>
+        <v>0.0302900101906893</v>
       </c>
       <c r="E271" t="s">
         <v>743</v>
@@ -34057,10 +34057,10 @@
         <v>745</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.505494505494506</v>
+        <v>-0.434065934065934</v>
       </c>
       <c r="D272" t="n">
-        <v>0.081215120725634</v>
+        <v>0.140406592788943</v>
       </c>
       <c r="E272" t="s">
         <v>743</v>
@@ -34074,10 +34074,10 @@
         <v>705</v>
       </c>
       <c r="C273" t="n">
-        <v>-0.510989010989011</v>
+        <v>-0.450549450549451</v>
       </c>
       <c r="D273" t="n">
-        <v>0.0775693109322543</v>
+        <v>0.124700833614222</v>
       </c>
       <c r="E273" t="s">
         <v>743</v>
@@ -34091,10 +34091,10 @@
         <v>746</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.252747252747253</v>
+        <v>-0.153846153846154</v>
       </c>
       <c r="D274" t="n">
-        <v>0.404328210459866</v>
+        <v>0.616791174982918</v>
       </c>
       <c r="E274" t="s">
         <v>743</v>
@@ -34108,10 +34108,10 @@
         <v>742</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.197802197802198</v>
+        <v>0.0824175824175824</v>
       </c>
       <c r="D275" t="n">
-        <v>0.517155182307656</v>
+        <v>0.792485539146813</v>
       </c>
       <c r="E275" t="s">
         <v>743</v>
@@ -34125,10 +34125,10 @@
         <v>744</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.269230769230769</v>
+        <v>-0.010989010989011</v>
       </c>
       <c r="D276" t="n">
-        <v>0.373300689357144</v>
+        <v>0.978311453941831</v>
       </c>
       <c r="E276" t="s">
         <v>743</v>
@@ -34142,10 +34142,10 @@
         <v>745</v>
       </c>
       <c r="C277" t="n">
-        <v>-0.148351648351648</v>
+        <v>0.0604395604395604</v>
       </c>
       <c r="D277" t="n">
-        <v>0.629758139870263</v>
+        <v>0.848988506886828</v>
       </c>
       <c r="E277" t="s">
         <v>743</v>
@@ -34159,10 +34159,10 @@
         <v>705</v>
       </c>
       <c r="C278" t="n">
-        <v>-0.043956043956044</v>
+        <v>0.208791208791209</v>
       </c>
       <c r="D278" t="n">
-        <v>0.891846567393224</v>
+        <v>0.493486137243575</v>
       </c>
       <c r="E278" t="s">
         <v>743</v>
@@ -34176,10 +34176,10 @@
         <v>746</v>
       </c>
       <c r="C279" t="n">
-        <v>-0.450549450549451</v>
+        <v>-0.186813186813187</v>
       </c>
       <c r="D279" t="n">
-        <v>0.124700833614222</v>
+        <v>0.541341049536417</v>
       </c>
       <c r="E279" t="s">
         <v>743</v>
@@ -34193,10 +34193,10 @@
         <v>742</v>
       </c>
       <c r="C280" t="n">
-        <v>-0.17032967032967</v>
+        <v>0.153846153846154</v>
       </c>
       <c r="D280" t="n">
-        <v>0.578544468706138</v>
+        <v>0.616791174982918</v>
       </c>
       <c r="E280" t="s">
         <v>743</v>
@@ -34210,10 +34210,10 @@
         <v>744</v>
       </c>
       <c r="C281" t="n">
-        <v>-0.5</v>
+        <v>-0.181318681318681</v>
       </c>
       <c r="D281" t="n">
-        <v>0.0849827627638607</v>
+        <v>0.553621558251875</v>
       </c>
       <c r="E281" t="s">
         <v>743</v>
@@ -34227,10 +34227,10 @@
         <v>745</v>
       </c>
       <c r="C282" t="n">
-        <v>-0.0384615384615385</v>
+        <v>0.247252747252747</v>
       </c>
       <c r="D282" t="n">
-        <v>0.906202123878284</v>
+        <v>0.414969916573171</v>
       </c>
       <c r="E282" t="s">
         <v>743</v>
@@ -34244,10 +34244,10 @@
         <v>705</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.186813186813187</v>
+        <v>0.10989010989011</v>
       </c>
       <c r="D283" t="n">
-        <v>0.541341049536417</v>
+        <v>0.723248148906413</v>
       </c>
       <c r="E283" t="s">
         <v>743</v>
@@ -34261,10 +34261,10 @@
         <v>746</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.252747252747253</v>
+        <v>0.0824175824175824</v>
       </c>
       <c r="D284" t="n">
-        <v>0.404328210459866</v>
+        <v>0.792485539146813</v>
       </c>
       <c r="E284" t="s">
         <v>743</v>
@@ -34278,10 +34278,10 @@
         <v>742</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.17032967032967</v>
+        <v>-0.346153846153846</v>
       </c>
       <c r="D285" t="n">
-        <v>0.578544468706138</v>
+        <v>0.247006583808201</v>
       </c>
       <c r="E285" t="s">
         <v>743</v>
@@ -34295,10 +34295,10 @@
         <v>744</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.631868131868132</v>
+        <v>-0.752747252747253</v>
       </c>
       <c r="D286" t="n">
-        <v>0.0237434280955737</v>
+        <v>0.00438717111438994</v>
       </c>
       <c r="E286" t="s">
         <v>743</v>
@@ -34312,10 +34312,10 @@
         <v>745</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.39010989010989</v>
+        <v>-0.478021978021978</v>
       </c>
       <c r="D287" t="n">
-        <v>0.188771716723795</v>
+        <v>0.101312257441764</v>
       </c>
       <c r="E287" t="s">
         <v>743</v>
@@ -34329,10 +34329,10 @@
         <v>705</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.538461538461538</v>
+        <v>-0.642857142857143</v>
       </c>
       <c r="D288" t="n">
-        <v>0.0610936374942774</v>
+        <v>0.0209018820886229</v>
       </c>
       <c r="E288" t="s">
         <v>743</v>
@@ -34346,10 +34346,10 @@
         <v>746</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.0989010989010989</v>
+        <v>-0.269230769230769</v>
       </c>
       <c r="D289" t="n">
-        <v>0.750730305659702</v>
+        <v>0.373300689357144</v>
       </c>
       <c r="E289" t="s">
         <v>743</v>
@@ -34383,7 +34383,7 @@
         <v>0.542255695829207</v>
       </c>
       <c r="D291" t="n">
-        <v>0.0451487952022555</v>
+        <v>0.0451487952022556</v>
       </c>
       <c r="E291" t="s">
         <v>706</v>
@@ -34519,7 +34519,7 @@
         <v>-0.522254461146982</v>
       </c>
       <c r="D299" t="n">
-        <v>0.0553927846994648</v>
+        <v>0.0553927846994649</v>
       </c>
       <c r="E299" t="s">
         <v>706</v>
@@ -35097,7 +35097,7 @@
         <v>0.60892647810329</v>
       </c>
       <c r="D333" t="n">
-        <v>0.02082047920339</v>
+        <v>0.0208204792033901</v>
       </c>
       <c r="E333" t="s">
         <v>706</v>
@@ -35335,7 +35335,7 @@
         <v>0.753379839697136</v>
       </c>
       <c r="D347" t="n">
-        <v>0.00186373302928311</v>
+        <v>0.00186373302928312</v>
       </c>
       <c r="E347" t="s">
         <v>706</v>
@@ -39279,7 +39279,7 @@
         <v>-0.701098901098901</v>
       </c>
       <c r="D579" t="n">
-        <v>0.00686211373106961</v>
+        <v>0.0068621137310696</v>
       </c>
       <c r="E579" t="s">
         <v>706</v>
@@ -39347,7 +39347,7 @@
         <v>-0.714285714285714</v>
       </c>
       <c r="D583" t="n">
-        <v>0.00556164999027656</v>
+        <v>0.00556164999027657</v>
       </c>
       <c r="E583" t="s">
         <v>706</v>
@@ -39874,7 +39874,7 @@
         <v>-0.714285714285714</v>
       </c>
       <c r="D614" t="n">
-        <v>0.00556164999027656</v>
+        <v>0.00556164999027657</v>
       </c>
       <c r="E614" t="s">
         <v>740</v>
@@ -40537,7 +40537,7 @@
         <v>-0.770426934790279</v>
       </c>
       <c r="D653" t="n">
-        <v>0.00126244758617328</v>
+        <v>0.00126244758617329</v>
       </c>
       <c r="E653" t="s">
         <v>740</v>
@@ -41472,7 +41472,7 @@
         <v>0.859340659340659</v>
       </c>
       <c r="D708" t="n">
-        <v>0.00006437554739319</v>
+        <v>0.0000643755473931896</v>
       </c>
       <c r="E708" t="s">
         <v>706</v>
